--- a/大金空調價格表_設備報價單.xlsx
+++ b/大金空調價格表_設備報價單.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hungys\Desktop\AI seed\test Google Sheets Connection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{827FE57C-CD8A-4C8A-852F-D38E0745251A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CEE029-1C03-45AA-95DA-D6A44EF9BDE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9648" tabRatio="920"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9645" tabRatio="830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRV設備價格表" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">VRV設備價格表!$A$1:$L$230</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">VRV設備價格表!$A$1:$O$289</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="522">
   <si>
     <t>BPMKS967A3</t>
   </si>
@@ -1804,19 +1805,247 @@
   </si>
   <si>
     <t>RXYQ28AHYLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用一對一室內機</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM28ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM22ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM36ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM41ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM50ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM60ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM71ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM80ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM90ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM22ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用一對一室外機</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM28ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM36ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM41ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM50ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM60ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM71ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM80ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RXM90ZVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>商用一對一室內機</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCA71CVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FBA71BVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>商用一對一室外機</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RZAC71DVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCA100CVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FBA100BVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RZAC100DVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCA125CVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FBA125BVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RZAC125DVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCA140CVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FBA140BVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RZAC140DVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用一對多室外機</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>4MXM110YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>3MXM90YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2MXM75YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2MXM56YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用一對多室內機</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM22YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM28YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM36YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM41YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM50YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM60YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM71YVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM80RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FTXM90RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FDXV22RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FDXV28RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FDXV36RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FDXV41RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FDXV50RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FDXV60RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FDXV71RVLT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>連接指數</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
-    <numFmt numFmtId="187" formatCode="#,##0.0_);\(#,##0.0\)"/>
-    <numFmt numFmtId="207" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="210" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="179" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -2140,7 +2369,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0"/>
     <xf numFmtId="37" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0"/>
@@ -2260,49 +2489,49 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="207" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="3" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2310,21 +2539,21 @@
     </xf>
   </cellXfs>
   <cellStyles count="15">
-    <cellStyle name="0,0_x000d__x000a_NA_x000d__x000a_" xfId="1"/>
-    <cellStyle name="BROAD SCOPE" xfId="2"/>
-    <cellStyle name="BROAD_SCOPE" xfId="3"/>
-    <cellStyle name="Comma(0)" xfId="4"/>
-    <cellStyle name="Comma(1)" xfId="5"/>
-    <cellStyle name="MEDIUM SCOPE" xfId="6"/>
-    <cellStyle name="NARROW SCOPE" xfId="7"/>
-    <cellStyle name="Rate_1" xfId="8"/>
-    <cellStyle name="Schedule" xfId="9"/>
+    <cellStyle name="0,0_x000d__x000a_NA_x000d__x000a_" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="BROAD SCOPE" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="BROAD_SCOPE" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Comma(0)" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Comma(1)" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="MEDIUM SCOPE" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="NARROW SCOPE" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Rate_1" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Schedule" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="10"/>
-    <cellStyle name="一般 3" xfId="11"/>
-    <cellStyle name="一般 4" xfId="12"/>
-    <cellStyle name="貨幣[0]_馬偕 11F VRV設備 " xfId="13"/>
-    <cellStyle name="樣式 1" xfId="14"/>
+    <cellStyle name="一般 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="一般 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="一般 4" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="貨幣[0]_馬偕 11F VRV設備 " xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="樣式 1" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2659,30 +2888,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L234"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <dimension ref="A1:O282"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="40" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="40" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="40" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="42.6640625" style="40" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="45" customWidth="1"/>
+    <col min="1" max="1" width="18.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.125" style="40" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="40" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="40" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="42.625" style="40" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.625" style="45" customWidth="1"/>
     <col min="8" max="8" width="21" style="11" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" style="46" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" style="44" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="34" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" style="40" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.875" style="46" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="44" customWidth="1"/>
+    <col min="11" max="11" width="15.25" style="34" customWidth="1"/>
+    <col min="12" max="12" width="18.75" style="40" hidden="1" customWidth="1"/>
     <col min="13" max="14" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="66" customHeight="1">
+    <row r="1" spans="1:15" ht="66" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>336</v>
       </c>
@@ -2719,8 +2948,11 @@
       <c r="L1" s="35" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="O1" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
         <v>340</v>
       </c>
@@ -2750,8 +2982,11 @@
       <c r="L2" s="40" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="O2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>340</v>
       </c>
@@ -2780,8 +3015,11 @@
       <c r="L3" s="40" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="O3" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3" t="s">
         <v>340</v>
       </c>
@@ -2810,8 +3048,11 @@
       <c r="L4" s="40" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="O4" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3" t="s">
         <v>340</v>
       </c>
@@ -2840,8 +3081,11 @@
       <c r="L5" s="40" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="O5" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3" t="s">
         <v>340</v>
       </c>
@@ -2870,8 +3114,11 @@
       <c r="L6" s="40" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="O6" s="1">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3" t="s">
         <v>340</v>
       </c>
@@ -2900,8 +3147,11 @@
       <c r="L7" s="40" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="O7" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
         <v>340</v>
       </c>
@@ -2930,8 +3180,11 @@
       <c r="L8" s="40" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="O8" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
         <v>340</v>
       </c>
@@ -2960,8 +3213,11 @@
       <c r="L9" s="40" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="O9" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
         <v>355</v>
       </c>
@@ -2997,7 +3253,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
         <v>355</v>
       </c>
@@ -3033,7 +3289,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
         <v>355</v>
       </c>
@@ -3069,7 +3325,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
         <v>355</v>
       </c>
@@ -3105,7 +3361,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
         <v>355</v>
       </c>
@@ -3132,7 +3388,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
         <v>355</v>
       </c>
@@ -3159,7 +3415,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
         <v>355</v>
       </c>
@@ -6157,7 +6413,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:15">
       <c r="A97" s="7" t="s">
         <v>355</v>
       </c>
@@ -6197,7 +6453,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:15">
       <c r="A98" s="7" t="s">
         <v>355</v>
       </c>
@@ -6237,7 +6493,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:15">
       <c r="A99" s="7" t="s">
         <v>355</v>
       </c>
@@ -6277,7 +6533,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:15">
       <c r="A100" s="7" t="s">
         <v>355</v>
       </c>
@@ -6317,7 +6573,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:15">
       <c r="A101" s="13" t="s">
         <v>364</v>
       </c>
@@ -6355,8 +6611,11 @@
       <c r="L101" s="40" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="102" spans="1:12">
+      <c r="O101" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
       <c r="A102" s="13" t="s">
         <v>364</v>
       </c>
@@ -6391,8 +6650,11 @@
       <c r="L102" s="40" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="103" spans="1:12">
+      <c r="O102" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
       <c r="A103" s="13" t="s">
         <v>364</v>
       </c>
@@ -6427,8 +6689,11 @@
       <c r="L103" s="40" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="104" spans="1:12">
+      <c r="O103" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
       <c r="A104" s="13" t="s">
         <v>364</v>
       </c>
@@ -6456,8 +6721,11 @@
       <c r="L104" s="40" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="105" spans="1:12">
+      <c r="O104" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
       <c r="A105" s="13" t="s">
         <v>364</v>
       </c>
@@ -6489,8 +6757,11 @@
       <c r="L105" s="40" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="106" spans="1:12">
+      <c r="O105" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
       <c r="A106" s="13" t="s">
         <v>364</v>
       </c>
@@ -6522,8 +6793,11 @@
       <c r="L106" s="40" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="107" spans="1:12">
+      <c r="O106" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
       <c r="A107" s="13" t="s">
         <v>364</v>
       </c>
@@ -6555,8 +6829,11 @@
       <c r="L107" s="40" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="108" spans="1:12">
+      <c r="O107" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
       <c r="A108" s="13" t="s">
         <v>364</v>
       </c>
@@ -6588,8 +6865,11 @@
       <c r="L108" s="40" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="109" spans="1:12">
+      <c r="O108" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
       <c r="A109" s="13" t="s">
         <v>364</v>
       </c>
@@ -6621,8 +6901,11 @@
       <c r="L109" s="40" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="110" spans="1:12">
+      <c r="O109" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
       <c r="A110" s="13" t="s">
         <v>364</v>
       </c>
@@ -6654,8 +6937,11 @@
       <c r="L110" s="40" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="111" spans="1:12">
+      <c r="O110" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
       <c r="A111" s="13" t="s">
         <v>364</v>
       </c>
@@ -6687,8 +6973,11 @@
       <c r="L111" s="40" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="112" spans="1:12" ht="15" customHeight="1">
+      <c r="O111" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="15" customHeight="1">
       <c r="A112" s="13" t="s">
         <v>364</v>
       </c>
@@ -6720,8 +7009,11 @@
       <c r="L112" s="40" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="113" spans="1:12">
+      <c r="O112" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
       <c r="A113" s="13" t="s">
         <v>364</v>
       </c>
@@ -6756,8 +7048,11 @@
       <c r="L113" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="114" spans="1:12">
+      <c r="O113" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
       <c r="A114" s="13" t="s">
         <v>364</v>
       </c>
@@ -6792,8 +7087,11 @@
       <c r="L114" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="115" spans="1:12">
+      <c r="O114" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
       <c r="A115" s="13" t="s">
         <v>364</v>
       </c>
@@ -6828,8 +7126,11 @@
       <c r="L115" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="116" spans="1:12">
+      <c r="O115" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
       <c r="A116" s="13" t="s">
         <v>364</v>
       </c>
@@ -6864,8 +7165,11 @@
       <c r="L116" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="117" spans="1:12">
+      <c r="O116" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
       <c r="A117" s="13" t="s">
         <v>364</v>
       </c>
@@ -6900,8 +7204,11 @@
       <c r="L117" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="118" spans="1:12">
+      <c r="O117" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
       <c r="A118" s="13" t="s">
         <v>364</v>
       </c>
@@ -6936,8 +7243,11 @@
       <c r="L118" s="40" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="119" spans="1:12">
+      <c r="O118" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
       <c r="A119" s="13" t="s">
         <v>364</v>
       </c>
@@ -6972,8 +7282,11 @@
       <c r="L119" s="40" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="120" spans="1:12">
+      <c r="O119" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
       <c r="A120" s="13" t="s">
         <v>364</v>
       </c>
@@ -7008,8 +7321,11 @@
       <c r="L120" s="40" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="121" spans="1:12">
+      <c r="O120" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
       <c r="A121" s="13" t="s">
         <v>364</v>
       </c>
@@ -7044,8 +7360,11 @@
       <c r="L121" s="40" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="122" spans="1:12">
+      <c r="O121" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
       <c r="A122" s="13" t="s">
         <v>364</v>
       </c>
@@ -7080,8 +7399,11 @@
       <c r="L122" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="123" spans="1:12">
+      <c r="O122" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
       <c r="A123" s="13" t="s">
         <v>364</v>
       </c>
@@ -7116,8 +7438,11 @@
       <c r="L123" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="124" spans="1:12">
+      <c r="O123" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
       <c r="A124" s="13" t="s">
         <v>364</v>
       </c>
@@ -7152,8 +7477,11 @@
       <c r="L124" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="125" spans="1:12">
+      <c r="O124" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
       <c r="A125" s="13" t="s">
         <v>364</v>
       </c>
@@ -7188,8 +7516,11 @@
       <c r="L125" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="126" spans="1:12">
+      <c r="O125" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
       <c r="A126" s="13" t="s">
         <v>364</v>
       </c>
@@ -7224,8 +7555,11 @@
       <c r="L126" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="127" spans="1:12">
+      <c r="O126" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
       <c r="A127" s="13" t="s">
         <v>364</v>
       </c>
@@ -7260,8 +7594,11 @@
       <c r="L127" s="40" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="128" spans="1:12">
+      <c r="O127" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
       <c r="A128" s="13" t="s">
         <v>364</v>
       </c>
@@ -7296,8 +7633,11 @@
       <c r="L128" s="51" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="129" spans="1:12">
+      <c r="O128" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
       <c r="A129" s="13" t="s">
         <v>364</v>
       </c>
@@ -7332,8 +7672,11 @@
       <c r="L129" s="40" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="130" spans="1:12">
+      <c r="O129" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
       <c r="A130" s="13" t="s">
         <v>364</v>
       </c>
@@ -7368,8 +7711,11 @@
       <c r="L130" s="40" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="131" spans="1:12">
+      <c r="O130" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
       <c r="A131" s="13" t="s">
         <v>364</v>
       </c>
@@ -7398,8 +7744,11 @@
       <c r="L131" s="40" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="132" spans="1:12">
+      <c r="O131" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
       <c r="A132" s="13" t="s">
         <v>364</v>
       </c>
@@ -7428,8 +7777,11 @@
       <c r="L132" s="40" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="133" spans="1:12">
+      <c r="O132" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
       <c r="A133" s="13" t="s">
         <v>364</v>
       </c>
@@ -7458,8 +7810,11 @@
       <c r="L133" s="40" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="134" spans="1:12">
+      <c r="O133" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
       <c r="A134" s="13" t="s">
         <v>364</v>
       </c>
@@ -7488,8 +7843,11 @@
       <c r="L134" s="40" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="135" spans="1:12">
+      <c r="O134" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
       <c r="A135" s="13" t="s">
         <v>364</v>
       </c>
@@ -7518,8 +7876,11 @@
       <c r="L135" s="40" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="136" spans="1:12">
+      <c r="O135" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
       <c r="A136" s="13" t="s">
         <v>364</v>
       </c>
@@ -7548,8 +7909,11 @@
       <c r="L136" s="40" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="137" spans="1:12">
+      <c r="O136" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
       <c r="A137" s="13" t="s">
         <v>364</v>
       </c>
@@ -7578,8 +7942,11 @@
       <c r="L137" s="40" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="138" spans="1:12">
+      <c r="O137" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
       <c r="A138" s="13" t="s">
         <v>364</v>
       </c>
@@ -7608,8 +7975,11 @@
       <c r="L138" s="40" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="139" spans="1:12">
+      <c r="O138" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
       <c r="A139" s="13" t="s">
         <v>364</v>
       </c>
@@ -7638,8 +8008,11 @@
       <c r="L139" s="40" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="140" spans="1:12">
+      <c r="O139" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
       <c r="A140" s="13" t="s">
         <v>364</v>
       </c>
@@ -7668,8 +8041,11 @@
       <c r="L140" s="40" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="141" spans="1:12">
+      <c r="O140" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
       <c r="A141" s="13" t="s">
         <v>364</v>
       </c>
@@ -7698,8 +8074,11 @@
       <c r="L141" s="40" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="142" spans="1:12">
+      <c r="O141" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
       <c r="A142" s="13" t="s">
         <v>364</v>
       </c>
@@ -7728,8 +8107,11 @@
       <c r="L142" s="40" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="143" spans="1:12">
+      <c r="O142" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
       <c r="A143" s="13" t="s">
         <v>364</v>
       </c>
@@ -7758,8 +8140,11 @@
       <c r="L143" s="40" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="144" spans="1:12">
+      <c r="O143" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
       <c r="A144" s="13" t="s">
         <v>364</v>
       </c>
@@ -7788,8 +8173,11 @@
       <c r="L144" s="40" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="145" spans="1:12">
+      <c r="O144" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
       <c r="A145" s="13" t="s">
         <v>364</v>
       </c>
@@ -7818,8 +8206,11 @@
       <c r="L145" s="40" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="146" spans="1:12">
+      <c r="O145" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
       <c r="A146" s="13" t="s">
         <v>364</v>
       </c>
@@ -7848,8 +8239,11 @@
       <c r="L146" s="40" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="147" spans="1:12">
+      <c r="O146" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
       <c r="A147" s="13" t="s">
         <v>364</v>
       </c>
@@ -7878,8 +8272,11 @@
       <c r="L147" s="40" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="148" spans="1:12">
+      <c r="O147" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15">
       <c r="A148" s="13" t="s">
         <v>364</v>
       </c>
@@ -7908,8 +8305,11 @@
       <c r="L148" s="40" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="149" spans="1:12">
+      <c r="O148" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
       <c r="A149" s="13" t="s">
         <v>364</v>
       </c>
@@ -7938,8 +8338,11 @@
       <c r="L149" s="40" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="150" spans="1:12">
+      <c r="O149" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
       <c r="A150" s="13" t="s">
         <v>364</v>
       </c>
@@ -7968,8 +8371,11 @@
       <c r="L150" s="40" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="151" spans="1:12">
+      <c r="O150" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
       <c r="A151" s="13" t="s">
         <v>364</v>
       </c>
@@ -7998,8 +8404,11 @@
       <c r="L151" s="40" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="152" spans="1:12">
+      <c r="O151" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
       <c r="A152" s="13" t="s">
         <v>364</v>
       </c>
@@ -8028,8 +8437,11 @@
       <c r="L152" s="40" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="153" spans="1:12">
+      <c r="O152" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
       <c r="A153" s="13" t="s">
         <v>364</v>
       </c>
@@ -8058,8 +8470,11 @@
       <c r="L153" s="40" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="154" spans="1:12">
+      <c r="O153" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
       <c r="A154" s="13" t="s">
         <v>364</v>
       </c>
@@ -8088,8 +8503,11 @@
       <c r="L154" s="40" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="155" spans="1:12">
+      <c r="O154" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15">
       <c r="A155" s="13" t="s">
         <v>364</v>
       </c>
@@ -8118,8 +8536,11 @@
       <c r="L155" s="40" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="156" spans="1:12">
+      <c r="O155" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15">
       <c r="A156" s="13" t="s">
         <v>364</v>
       </c>
@@ -8148,8 +8569,11 @@
       <c r="L156" s="40" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="157" spans="1:12">
+      <c r="O156" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
       <c r="A157" s="13" t="s">
         <v>364</v>
       </c>
@@ -8178,8 +8602,11 @@
       <c r="L157" s="40" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="158" spans="1:12">
+      <c r="O157" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
       <c r="A158" s="13" t="s">
         <v>364</v>
       </c>
@@ -8208,8 +8635,11 @@
       <c r="L158" s="40" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="159" spans="1:12">
+      <c r="O158" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
       <c r="A159" s="13" t="s">
         <v>364</v>
       </c>
@@ -8238,8 +8668,11 @@
       <c r="L159" s="40" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="160" spans="1:12">
+      <c r="O159" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
       <c r="A160" s="13" t="s">
         <v>364</v>
       </c>
@@ -8268,8 +8701,11 @@
       <c r="L160" s="40" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="161" spans="1:12">
+      <c r="O160" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
       <c r="A161" s="13" t="s">
         <v>364</v>
       </c>
@@ -8298,8 +8734,11 @@
       <c r="L161" s="40" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="162" spans="1:12">
+      <c r="O161" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
       <c r="A162" s="13" t="s">
         <v>364</v>
       </c>
@@ -8328,8 +8767,11 @@
       <c r="L162" s="40" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="163" spans="1:12">
+      <c r="O162" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
       <c r="A163" s="13" t="s">
         <v>364</v>
       </c>
@@ -8358,8 +8800,11 @@
       <c r="L163" s="40" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="164" spans="1:12">
+      <c r="O163" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
       <c r="A164" s="13" t="s">
         <v>364</v>
       </c>
@@ -8388,8 +8833,11 @@
       <c r="L164" s="40" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="165" spans="1:12">
+      <c r="O164" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
       <c r="A165" s="13" t="s">
         <v>364</v>
       </c>
@@ -8418,8 +8866,11 @@
       <c r="L165" s="40" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="166" spans="1:12">
+      <c r="O165" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
       <c r="A166" s="13" t="s">
         <v>364</v>
       </c>
@@ -8448,8 +8899,11 @@
       <c r="L166" s="40" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="167" spans="1:12">
+      <c r="O166" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15">
       <c r="A167" s="13" t="s">
         <v>364</v>
       </c>
@@ -8478,8 +8932,11 @@
       <c r="L167" s="40" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="168" spans="1:12">
+      <c r="O167" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15">
       <c r="A168" s="13" t="s">
         <v>364</v>
       </c>
@@ -8509,8 +8966,11 @@
       <c r="L168" s="40" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="169" spans="1:12">
+      <c r="O168" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15">
       <c r="A169" s="13" t="s">
         <v>364</v>
       </c>
@@ -8539,8 +8999,11 @@
       <c r="L169" s="40" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="170" spans="1:12">
+      <c r="O169" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15">
       <c r="A170" s="13" t="s">
         <v>364</v>
       </c>
@@ -8569,8 +9032,11 @@
       <c r="L170" s="40" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="171" spans="1:12">
+      <c r="O170" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15">
       <c r="A171" s="13" t="s">
         <v>364</v>
       </c>
@@ -8600,8 +9066,11 @@
       <c r="L171" s="40" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="172" spans="1:12">
+      <c r="O171" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
       <c r="A172" s="13" t="s">
         <v>364</v>
       </c>
@@ -8631,8 +9100,11 @@
       <c r="L172" s="40" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="173" spans="1:12">
+      <c r="O172" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
       <c r="A173" s="13" t="s">
         <v>364</v>
       </c>
@@ -8662,8 +9134,11 @@
       <c r="L173" s="40" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="174" spans="1:12">
+      <c r="O173" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
       <c r="A174" s="13" t="s">
         <v>364</v>
       </c>
@@ -8693,8 +9168,11 @@
       <c r="L174" s="40" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="175" spans="1:12">
+      <c r="O174" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
       <c r="A175" s="13" t="s">
         <v>364</v>
       </c>
@@ -8723,8 +9201,11 @@
       <c r="L175" s="40" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="176" spans="1:12">
+      <c r="O175" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15">
       <c r="A176" s="13" t="s">
         <v>364</v>
       </c>
@@ -8753,8 +9234,11 @@
       <c r="L176" s="40" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="177" spans="1:12" ht="15.75" customHeight="1">
+      <c r="O176" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" ht="15.75" customHeight="1">
       <c r="A177" s="13" t="s">
         <v>364</v>
       </c>
@@ -8783,8 +9267,11 @@
       <c r="L177" s="40" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="178" spans="1:12">
+      <c r="O177" s="1">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15">
       <c r="A178" s="13" t="s">
         <v>364</v>
       </c>
@@ -8813,8 +9300,11 @@
       <c r="L178" s="40" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="179" spans="1:12">
+      <c r="O178" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15">
       <c r="A179" s="13" t="s">
         <v>364</v>
       </c>
@@ -8843,8 +9333,11 @@
       <c r="L179" s="40" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="180" spans="1:12">
+      <c r="O179" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15">
       <c r="A180" s="13" t="s">
         <v>364</v>
       </c>
@@ -8873,8 +9366,11 @@
       <c r="L180" s="40" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="181" spans="1:12">
+      <c r="O180" s="1">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15">
       <c r="A181" s="24" t="s">
         <v>403</v>
       </c>
@@ -8901,7 +9397,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="182" spans="1:12">
+    <row r="182" spans="1:15">
       <c r="A182" s="24" t="s">
         <v>403</v>
       </c>
@@ -8928,7 +9424,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="183" spans="1:12">
+    <row r="183" spans="1:15">
       <c r="A183" s="24" t="s">
         <v>403</v>
       </c>
@@ -8958,7 +9454,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="184" spans="1:12">
+    <row r="184" spans="1:15">
       <c r="A184" s="24" t="s">
         <v>403</v>
       </c>
@@ -8988,7 +9484,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="185" spans="1:12">
+    <row r="185" spans="1:15">
       <c r="A185" s="24" t="s">
         <v>403</v>
       </c>
@@ -9018,7 +9514,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="186" spans="1:12">
+    <row r="186" spans="1:15">
       <c r="A186" s="24" t="s">
         <v>403</v>
       </c>
@@ -9048,7 +9544,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="187" spans="1:12">
+    <row r="187" spans="1:15">
       <c r="A187" s="24" t="s">
         <v>403</v>
       </c>
@@ -9078,7 +9574,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="188" spans="1:12">
+    <row r="188" spans="1:15">
       <c r="A188" s="24" t="s">
         <v>403</v>
       </c>
@@ -9108,7 +9604,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="189" spans="1:12">
+    <row r="189" spans="1:15">
       <c r="A189" s="24" t="s">
         <v>403</v>
       </c>
@@ -9138,7 +9634,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="190" spans="1:12">
+    <row r="190" spans="1:15">
       <c r="A190" s="24" t="s">
         <v>403</v>
       </c>
@@ -9168,7 +9664,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="191" spans="1:12">
+    <row r="191" spans="1:15">
       <c r="A191" s="24" t="s">
         <v>403</v>
       </c>
@@ -9195,7 +9691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12">
+    <row r="192" spans="1:15">
       <c r="A192" s="24" t="s">
         <v>403</v>
       </c>
@@ -10350,23 +10846,475 @@
       </c>
     </row>
     <row r="231" spans="1:11">
+      <c r="A231" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C231" s="40" t="s">
+        <v>467</v>
+      </c>
       <c r="E231" s="41"/>
-      <c r="G231" s="43"/>
+      <c r="G231" s="43">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
     <row r="232" spans="1:11">
+      <c r="A232" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C232" s="40" t="s">
+        <v>466</v>
+      </c>
       <c r="E232" s="41"/>
+      <c r="G232" s="45">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="233" spans="1:11">
+      <c r="A233" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C233" s="40" t="s">
+        <v>468</v>
+      </c>
       <c r="E233" s="41"/>
+      <c r="G233" s="45">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="234" spans="1:11">
+      <c r="A234" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C234" s="40" t="s">
+        <v>469</v>
+      </c>
       <c r="E234" s="41"/>
+      <c r="G234" s="45">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="A235" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C235" s="40" t="s">
+        <v>470</v>
+      </c>
+      <c r="G235" s="45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11">
+      <c r="A236" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C236" s="40" t="s">
+        <v>471</v>
+      </c>
+      <c r="G236" s="45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="A237" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C237" s="40" t="s">
+        <v>472</v>
+      </c>
+      <c r="G237" s="45">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11">
+      <c r="A238" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C238" s="40" t="s">
+        <v>473</v>
+      </c>
+      <c r="G238" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11">
+      <c r="A239" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C239" s="40" t="s">
+        <v>474</v>
+      </c>
+      <c r="G239" s="45">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11">
+      <c r="A240" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C240" s="40" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C241" s="40" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C242" s="40" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C243" s="40" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C244" s="40" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C245" s="40" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C246" s="40" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C247" s="40" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C248" s="40" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C249" s="40" t="s">
+        <v>486</v>
+      </c>
+      <c r="G249" s="45">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C250" s="40" t="s">
+        <v>487</v>
+      </c>
+      <c r="G250" s="45">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C251" s="40" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C252" s="40" t="s">
+        <v>490</v>
+      </c>
+      <c r="G252" s="45">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C253" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="G253" s="45">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C254" s="40" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C255" s="40" t="s">
+        <v>493</v>
+      </c>
+      <c r="G255" s="45">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C256" s="40" t="s">
+        <v>494</v>
+      </c>
+      <c r="G256" s="45">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C257" s="40" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C258" s="40" t="s">
+        <v>496</v>
+      </c>
+      <c r="G258" s="45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C259" s="40" t="s">
+        <v>497</v>
+      </c>
+      <c r="G259" s="45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C260" s="40" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C261" s="40" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C262" s="40" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C263" s="40" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C264" s="40" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C265" s="40" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C266" s="40" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C267" s="40" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C268" s="40" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C269" s="40" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C270" s="40" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C271" s="40" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C272" s="40" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C273" s="40" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C274" s="40" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C275" s="40" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C276" s="40" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C277" s="40" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C278" s="40" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C279" s="40" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C280" s="40" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" s="1" t="s">
+        <v>504</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L230"/>
+  <autoFilter ref="A1:L230" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="81" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="96" max="16383" man="1"/>
     <brk id="115" max="16383" man="1"/>

--- a/大金空調價格表_設備報價單.xlsx
+++ b/大金空調價格表_設備報價單.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hungys\Desktop\AI seed\test Google Sheets Connection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CEE029-1C03-45AA-95DA-D6A44EF9BDE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B1E69C-C64B-41A6-BCB7-2D05AD5CE8A4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9645" tabRatio="830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9648" tabRatio="830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRV設備價格表" sheetId="11" r:id="rId1"/>
@@ -2893,20 +2893,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O282"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="18.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.125" style="40" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="40" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="40" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="42.625" style="40" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.625" style="45" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="40" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="40" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="40" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="42.6640625" style="40" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="45" customWidth="1"/>
     <col min="8" max="8" width="21" style="11" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="15.875" style="46" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="44" customWidth="1"/>
-    <col min="11" max="11" width="15.25" style="34" customWidth="1"/>
-    <col min="12" max="12" width="18.75" style="40" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" style="46" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" style="44" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="34" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" style="40" hidden="1" customWidth="1"/>
     <col min="13" max="14" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
@@ -11179,6 +11179,9 @@
       <c r="C265" s="40" t="s">
         <v>505</v>
       </c>
+      <c r="G265" s="43">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="1" t="s">
@@ -11187,6 +11190,9 @@
       <c r="C266" s="40" t="s">
         <v>506</v>
       </c>
+      <c r="G266" s="45">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="1" t="s">
@@ -11195,6 +11201,9 @@
       <c r="C267" s="40" t="s">
         <v>507</v>
       </c>
+      <c r="G267" s="45">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" s="1" t="s">
@@ -11203,6 +11212,9 @@
       <c r="C268" s="40" t="s">
         <v>508</v>
       </c>
+      <c r="G268" s="45">
+        <v>4.0999999999999996</v>
+      </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" s="1" t="s">
@@ -11211,6 +11223,9 @@
       <c r="C269" s="40" t="s">
         <v>509</v>
       </c>
+      <c r="G269" s="45">
+        <v>5</v>
+      </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" s="1" t="s">
@@ -11219,6 +11234,9 @@
       <c r="C270" s="40" t="s">
         <v>510</v>
       </c>
+      <c r="G270" s="45">
+        <v>6</v>
+      </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="1" t="s">
@@ -11227,6 +11245,9 @@
       <c r="C271" s="40" t="s">
         <v>511</v>
       </c>
+      <c r="G271" s="45">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" s="1" t="s">
@@ -11235,77 +11256,104 @@
       <c r="C272" s="40" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="273" spans="1:3">
+      <c r="G272" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C273" s="40" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="274" spans="1:3">
+      <c r="G273" s="45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
       <c r="A274" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C274" s="40" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="275" spans="1:3">
+      <c r="G274" s="43">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C275" s="40" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="276" spans="1:3">
+      <c r="G275" s="45">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C276" s="40" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="277" spans="1:3">
+      <c r="G276" s="45">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C277" s="40" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="278" spans="1:3">
+      <c r="G277" s="45">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C278" s="40" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="279" spans="1:3">
+      <c r="G278" s="45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C279" s="40" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="280" spans="1:3">
+      <c r="G279" s="45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" s="1" t="s">
         <v>504</v>
       </c>
       <c r="C280" s="40" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="281" spans="1:3">
+      <c r="G280" s="45">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" s="1" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:7">
       <c r="A282" s="1" t="s">
         <v>504</v>
       </c>
@@ -11314,7 +11362,7 @@
   <autoFilter ref="A1:L230" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="81" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="96" max="16383" man="1"/>
     <brk id="115" max="16383" man="1"/>
